--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488186_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488186_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0402</v>
+        <v>5.9348</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3408</v>
+        <v>6.9398</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3005</v>
+        <v>-1.0051</v>
       </c>
       <c r="G2" t="n">
         <v>6.3754</v>
@@ -610,13 +610,13 @@
         <v>1.1117</v>
       </c>
       <c r="S2" t="n">
-        <v>0.054</v>
+        <v>0.9485</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0161</v>
+        <v>0.5829</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0701</v>
+        <v>0.3656</v>
       </c>
       <c r="V2" t="n">
         <v>-1.5744</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5021</v>
+        <v>4.4946</v>
       </c>
       <c r="E3" t="n">
-        <v>2.307</v>
+        <v>3.004</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1951</v>
+        <v>1.4906</v>
       </c>
       <c r="G3" t="n">
         <v>2.4233</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4596</v>
+        <v>0.5329</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2437</v>
+        <v>0.4533</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2159</v>
+        <v>0.0796</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3144</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KALLE</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6966</v>
+        <v>2.8793</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3832</v>
+        <v>2.6908</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3134</v>
+        <v>0.1885</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8563</v>
+        <v>4.2913</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5583</v>
+        <v>1.998</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2981</v>
+        <v>2.2932</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0973</v>
+        <v>5.6771</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1849</v>
+        <v>2.8772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9124</v>
+        <v>2.7999</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.241</v>
+        <v>-1.3858</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6267</v>
+        <v>-0.8791</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6143</v>
+        <v>-0.5067</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-3.5205</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8529</v>
+        <v>-4.6322</v>
       </c>
       <c r="R4" t="n">
-        <v>1.297</v>
+        <v>1.1117</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0255</v>
+        <v>0.8496</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4537</v>
+        <v>0.3871</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5718</v>
+        <v>0.4626</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.315</v>
+        <v>1.2589</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>L. RAMOS CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1916</v>
+        <v>1.5755</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3971</v>
+        <v>-1.5475</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2055</v>
+        <v>3.123</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2913</v>
+        <v>0.7809</v>
       </c>
       <c r="H5" t="n">
-        <v>1.998</v>
+        <v>1.6887</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2932</v>
+        <v>-0.9078000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>5.6771</v>
+        <v>-0.4122</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8772</v>
+        <v>0.8414</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7999</v>
+        <v>-1.2536</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3858</v>
+        <v>1.193</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8791</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5067</v>
+        <v>0.3457</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.5205</v>
+        <v>-1.297</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.6322</v>
+        <v>-2.7793</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1117</v>
+        <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1619</v>
+        <v>0.5189</v>
       </c>
       <c r="T5" t="n">
-        <v>0.09329999999999999</v>
+        <v>0.0712</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.4476</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2589</v>
+        <v>1.5727</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2589</v>
+        <v>1.5727</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. LEÓN TEJERA</t>
+          <t>S. KALLE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2441</v>
+        <v>1.505</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2441</v>
+        <v>0.8071</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.6979</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2441</v>
+        <v>0.8563</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.5583</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2441</v>
+        <v>0.2981</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2441</v>
+        <v>2.0973</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.1849</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2441</v>
+        <v>0.9124</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.241</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.6267</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.6143</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.8339</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>0.8776</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.9563</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. LEON TEJERA</t>
+          <t>B. LEÓN TEJERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2273</v>
+        <v>1.2441</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0413</v>
+        <v>1.2441</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2686</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.324</v>
+        <v>1.2441</v>
       </c>
       <c r="H7" t="n">
-        <v>0.773</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0969</v>
+        <v>1.2441</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.363</v>
+        <v>1.2441</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1027</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.4657</v>
+        <v>1.2441</v>
       </c>
       <c r="M7" t="n">
-        <v>1.039</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6703</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3687</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7546</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0073</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2527</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. RAMOS CASTRO</t>
+          <t>B. LEON TEJERA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9283</v>
+        <v>1.1666</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3424</v>
+        <v>-1.3236</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2707</v>
+        <v>2.4902</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7809</v>
+        <v>-1.324</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6887</v>
+        <v>0.773</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-2.0969</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4122</v>
+        <v>-2.363</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8414</v>
+        <v>0.1027</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2536</v>
+        <v>-2.4657</v>
       </c>
       <c r="M8" t="n">
-        <v>1.193</v>
+        <v>1.039</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.6703</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3457</v>
+        <v>0.3687</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.297</v>
+        <v>1.4823</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.4823</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1283</v>
+        <v>0.6939</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7237</v>
+        <v>0.725</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5954</v>
+        <v>-0.0311</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5727</v>
+        <v>0.3144</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5727</v>
+        <v>0.3144</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>J. SÁNCHEZ RENA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8348</v>
+        <v>0.6221</v>
       </c>
       <c r="E9" t="n">
-        <v>1.771</v>
+        <v>0.6221</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9362</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3172</v>
+        <v>0.6221</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3617</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9555</v>
+        <v>0.6221</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7219</v>
+        <v>0.6221</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5039</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.218</v>
+        <v>0.6221</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5953000000000001</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1421</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.7374000000000001</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.7057</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.0519</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6891</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SÁNCHEZ RENA</t>
+          <t>S. KVERNADZE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6221</v>
+        <v>0.4266</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6221</v>
+        <v>-0.1733</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.5999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6221</v>
+        <v>-2.016</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.6963</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6221</v>
+        <v>-1.3197</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6221</v>
+        <v>-1.2132</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>-0.1161</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6221</v>
+        <v>-1.0971</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-0.8028</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.5803</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2226</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.297</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.1456</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.0399</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.1057</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. KVERNADZE</t>
+          <t>J. SANCHEZ RENA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2975</v>
+        <v>0.2649</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.13</v>
+        <v>0.8994</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4275</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.016</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6963</v>
+        <v>-0.1468</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.3197</v>
+        <v>0.1474</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2132</v>
+        <v>0.7372</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1161</v>
+        <v>0.0215</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0971</v>
+        <v>0.7157</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8028</v>
+        <v>-0.7366</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5803</v>
+        <v>-0.1683</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2226</v>
+        <v>-0.5683</v>
       </c>
       <c r="P11" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0165</v>
+        <v>0.2643</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0831</v>
+        <v>0.1623</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0667</v>
+        <v>0.102</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. CISSE</t>
+          <t>S. GALIANO AVILA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1642</v>
+        <v>0.0347</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2891</v>
+        <v>-0.8032</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1248</v>
+        <v>0.8379</v>
       </c>
       <c r="G12" t="n">
-        <v>1.5848</v>
+        <v>-0.513</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5901999999999999</v>
+        <v>-1.1183</v>
       </c>
       <c r="I12" t="n">
-        <v>2.175</v>
+        <v>0.6052</v>
       </c>
       <c r="J12" t="n">
-        <v>1.874</v>
+        <v>-1.1369</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9152</v>
+        <v>-1.2198</v>
       </c>
       <c r="L12" t="n">
-        <v>2.7893</v>
+        <v>0.0829</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.2893</v>
+        <v>0.6239</v>
       </c>
       <c r="N12" t="n">
-        <v>0.325</v>
+        <v>0.1016</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6143</v>
+        <v>0.5223</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1533</v>
+        <v>0.5652</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8979</v>
+        <v>0.0193</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2554</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.2033</v>
+        <v>-0.9439</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.63</v>
+        <v>0.3144</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5733</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. GALIANO AVILA</t>
+          <t>S. CISSE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1535</v>
+        <v>0.0291</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0537</v>
+        <v>0.1047</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2072</v>
+        <v>-0.0756</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.513</v>
+        <v>1.5848</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1183</v>
+        <v>-0.5901999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6052</v>
+        <v>2.175</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1369</v>
+        <v>1.874</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2198</v>
+        <v>-0.9152</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0829</v>
+        <v>2.7893</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6239</v>
+        <v>-0.2893</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1016</v>
+        <v>0.325</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5223</v>
+        <v>-0.6143</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6839</v>
+        <v>1.0181</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2313</v>
+        <v>0.7135</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9152</v>
+        <v>0.3046</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.9439</v>
+        <v>-2.2033</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3144</v>
+        <v>-0.63</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2583</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. SANCHEZ RENA</t>
+          <t>S. CASAS GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0936</v>
+        <v>-0.3015</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7036</v>
+        <v>-0.5399</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.61</v>
+        <v>0.2385</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.9809</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1468</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1474</v>
+        <v>-0.1597</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7372</v>
+        <v>-0.5284</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0215</v>
+        <v>-0.6529</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7157</v>
+        <v>0.1244</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7366</v>
+        <v>-0.4524</v>
       </c>
       <c r="N14" t="n">
         <v>-0.1683</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5683</v>
+        <v>-0.2841</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1546,28 +1546,28 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.093</v>
+        <v>0.0494</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0336</v>
+        <v>-0.0115</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1266</v>
+        <v>0.0609</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CASAS GARCIA</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3502</v>
+        <v>-0.4093</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6379</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2877</v>
+        <v>-1.1578</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9809</v>
+        <v>4.3172</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8211000000000001</v>
+        <v>3.3617</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1597</v>
+        <v>0.9555</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5284</v>
+        <v>3.7219</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6529</v>
+        <v>3.5039</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1244</v>
+        <v>0.218</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4524</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1683</v>
+        <v>-0.1421</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2841</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-3.7057</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0007</v>
+        <v>1.4969</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1094</v>
+        <v>1.0294</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1102</v>
+        <v>0.4675</v>
       </c>
       <c r="V15" t="n">
-        <v>0.63</v>
+        <v>-2.5177</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X15" t="n">
-        <v>0.63</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="16">
@@ -1657,19 +1657,19 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>18.6457</v>
+        <v>19.4665</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8527</v>
+        <v>12.673</v>
       </c>
       <c r="F16" t="n">
-        <v>6.793200000000001</v>
+        <v>6.793400000000001</v>
       </c>
       <c r="G16" t="n">
         <v>17.6621</v>
       </c>
       <c r="H16" t="n">
-        <v>5.643599999999998</v>
+        <v>5.643600000000001</v>
       </c>
       <c r="I16" t="n">
         <v>12.0186</v>
@@ -1690,7 +1690,7 @@
         <v>-2.1177</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6901</v>
+        <v>-0.6901000000000002</v>
       </c>
       <c r="P16" t="n">
         <v>-3.7058</v>
@@ -1702,16 +1702,16 @@
         <v>12.97</v>
       </c>
       <c r="S16" t="n">
-        <v>9.096500000000001</v>
+        <v>9.917199999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>5.2294</v>
+        <v>6.050000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>3.8671</v>
+        <v>3.8672</v>
       </c>
       <c r="V16" t="n">
-        <v>-4.407100000000001</v>
+        <v>-4.4071</v>
       </c>
       <c r="W16" t="n">
         <v>2.8293</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.336</v>
+        <v>3.0657</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1828</v>
+        <v>2.6932</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1531</v>
+        <v>0.3725</v>
       </c>
       <c r="G17" t="n">
         <v>0.9888</v>
@@ -1780,13 +1780,13 @@
         <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5504</v>
+        <v>0.2801</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7461</v>
+        <v>0.2565</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1958</v>
+        <v>0.0236</v>
       </c>
       <c r="V17" t="n">
         <v>0.3144</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8323</v>
+        <v>2.9693</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5578</v>
+        <v>2.3619</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2745</v>
+        <v>0.6073</v>
       </c>
       <c r="G18" t="n">
         <v>2.6783</v>
@@ -1858,13 +1858,13 @@
         <v>3.1499</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1784</v>
+        <v>-1.0415</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6392</v>
+        <v>-0.835</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5392</v>
+        <v>-0.2065</v>
       </c>
       <c r="V18" t="n">
         <v>1.8883</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. VICENTE GARCÍA</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6221</v>
+        <v>1.5207</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6221</v>
+        <v>3.9523</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-2.4317</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6221</v>
+        <v>0.6278</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>2.5708</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6221</v>
+        <v>-1.943</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6221</v>
+        <v>5.5373</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.1782</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6221</v>
+        <v>1.3591</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-4.9095</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-1.6074</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-3.3021</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-1.5159</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.955</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.5609</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.63</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>S. VICENTE GARCÍA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1806</v>
+        <v>0.6221</v>
       </c>
       <c r="E21" t="n">
-        <v>3.5606</v>
+        <v>0.6221</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.38</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6278</v>
+        <v>0.6221</v>
       </c>
       <c r="H21" t="n">
-        <v>2.5708</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.943</v>
+        <v>0.6221</v>
       </c>
       <c r="J21" t="n">
-        <v>5.5373</v>
+        <v>0.6221</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1782</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3591</v>
+        <v>0.6221</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.9095</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6074</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.3021</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8559</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3467</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.5092</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1975</v>
+        <v>0.1048</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8204</v>
+        <v>0.9183</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0179</v>
+        <v>-0.8135</v>
       </c>
       <c r="G22" t="n">
         <v>0.3638</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5613</v>
+        <v>-0.259</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2189</v>
+        <v>-0.1209</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3425</v>
+        <v>-0.138</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.478</v>
+        <v>-1.8451</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7955</v>
+        <v>-1.1873</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6824</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8525</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3746</v>
+        <v>0.0075</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4887</v>
+        <v>0.097</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6535</v>
+        <v>-2.1879</v>
       </c>
       <c r="E24" t="n">
         <v>-1.7386</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.9149</v>
+        <v>-0.4493</v>
       </c>
       <c r="G24" t="n">
         <v>-3.9271</v>
@@ -2326,13 +2326,13 @@
         <v>2.2234</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6708</v>
+        <v>-0.2052</v>
       </c>
       <c r="T24" t="n">
         <v>-0.2014</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4693</v>
+        <v>-0.0037</v>
       </c>
       <c r="V24" t="n">
         <v>1.5738</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6586</v>
+        <v>-2.8826</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1457</v>
+        <v>-3.754</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4871</v>
+        <v>0.8714</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7954</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9749</v>
+        <v>-0.199</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7996</v>
+        <v>-0.4079</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1754</v>
+        <v>0.2089</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2589</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.8526</v>
+        <v>-3.1659</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7935</v>
+        <v>-2.6956</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.0591</v>
+        <v>-0.4704</v>
       </c>
       <c r="G26" t="n">
         <v>-4.3039</v>
@@ -2482,13 +2482,13 @@
         <v>2.594</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5487</v>
+        <v>-0.8621</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8244</v>
+        <v>-0.7265</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.1356</v>
       </c>
       <c r="V26" t="n">
         <v>1.2589</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.5501</v>
+        <v>-3.7094</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8654</v>
+        <v>-1.5716</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.6847</v>
+        <v>-2.1378</v>
       </c>
       <c r="G27" t="n">
         <v>-1.4442</v>
@@ -2560,13 +2560,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.5293</v>
+        <v>-0.6886</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.6354</v>
+        <v>-0.3416</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.8939</v>
+        <v>-0.347</v>
       </c>
       <c r="V27" t="n">
         <v>1.5733</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-5.2797</v>
+        <v>-5.1256</v>
       </c>
       <c r="E28" t="n">
-        <v>-4.1584</v>
+        <v>-3.9625</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1213</v>
+        <v>-1.1631</v>
       </c>
       <c r="G28" t="n">
         <v>-4.1933</v>
@@ -2638,13 +2638,13 @@
         <v>1.297</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.656</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.7449</v>
+        <v>-0.549</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.107</v>
       </c>
       <c r="V28" t="n">
         <v>-1.5733</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.1572</v>
+        <v>-6.3049</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.2502</v>
+        <v>-4.6419</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.907</v>
+        <v>-1.6631</v>
       </c>
       <c r="G29" t="n">
         <v>-7.6368</v>
@@ -2716,13 +2716,13 @@
         <v>1.6676</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1079</v>
+        <v>-0.0398</v>
       </c>
       <c r="T29" t="n">
-        <v>0.3084</v>
+        <v>-0.0833</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.2005</v>
+        <v>0.0435</v>
       </c>
       <c r="V29" t="n">
         <v>0.6304999999999999</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-18.6459</v>
+        <v>-14.7285</v>
       </c>
       <c r="E30" t="n">
-        <v>-6.7933</v>
+        <v>-6.793399999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.8526</v>
+        <v>-7.9355</v>
       </c>
       <c r="G30" t="n">
         <v>-17.6621</v>
@@ -2794,13 +2794,13 @@
         <v>16.6758</v>
       </c>
       <c r="S30" t="n">
-        <v>-9.096400000000001</v>
+        <v>-5.179499999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>-3.8673</v>
+        <v>-3.8671</v>
       </c>
       <c r="U30" t="n">
-        <v>-5.229500000000001</v>
+        <v>-1.3122</v>
       </c>
       <c r="V30" t="n">
         <v>4.407</v>
